--- a/backend/src/main/resources/templates/template.xlsx
+++ b/backend/src/main/resources/templates/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\1\IdeaProjects\Schedule\backend\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6622D19E-0274-4049-845C-3648FB202A84}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E426632B-3B3E-4415-B22D-4D689E44CC42}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4905" yWindow="15" windowWidth="27075" windowHeight="20550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="450" windowWidth="27075" windowHeight="20550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Расписание" sheetId="1" r:id="rId1"/>
@@ -642,7 +642,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -769,17 +769,29 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -814,33 +826,22 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1125,7 +1126,7 @@
   <sheetPr codeName="Лист1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BK96"/>
+  <dimension ref="A1:BK117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.42578125" customWidth="1"/>
@@ -1187,8 +1188,8 @@
       </c>
       <c r="L2" s="11"/>
       <c r="M2" s="10"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
+      <c r="N2" s="62"/>
+      <c r="O2" s="62"/>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
@@ -1226,8 +1227,8 @@
       </c>
       <c r="L3" s="10"/>
       <c r="M3" s="10"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
+      <c r="N3" s="62"/>
+      <c r="O3" s="62"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
@@ -1237,9 +1238,9 @@
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
-      <c r="W3" s="60"/>
-      <c r="X3" s="61"/>
-      <c r="Y3" s="62"/>
+      <c r="W3" s="64"/>
+      <c r="X3" s="65"/>
+      <c r="Y3" s="66"/>
       <c r="Z3" s="10"/>
       <c r="AA3" s="10"/>
       <c r="AB3" s="10"/>
@@ -1264,8 +1265,8 @@
       </c>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="10"/>
       <c r="R4" s="10"/>
@@ -1390,50 +1391,50 @@
       <c r="C6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="51" t="s">
+      <c r="D6" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="51" t="s">
+      <c r="E6" s="70"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="71"/>
+      <c r="H6" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="51" t="s">
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="71"/>
+      <c r="L6" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="53"/>
-      <c r="Q6" s="51" t="s">
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
+      <c r="P6" s="71"/>
+      <c r="Q6" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="52"/>
-      <c r="S6" s="52"/>
-      <c r="T6" s="53"/>
-      <c r="U6" s="51" t="s">
+      <c r="R6" s="70"/>
+      <c r="S6" s="70"/>
+      <c r="T6" s="71"/>
+      <c r="U6" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="52"/>
-      <c r="W6" s="52"/>
-      <c r="X6" s="53"/>
-      <c r="Y6" s="51" t="s">
+      <c r="V6" s="70"/>
+      <c r="W6" s="70"/>
+      <c r="X6" s="71"/>
+      <c r="Y6" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="Z6" s="52"/>
-      <c r="AA6" s="52"/>
-      <c r="AB6" s="52"/>
-      <c r="AC6" s="53"/>
-      <c r="AD6" s="50" t="s">
+      <c r="Z6" s="70"/>
+      <c r="AA6" s="70"/>
+      <c r="AB6" s="70"/>
+      <c r="AC6" s="71"/>
+      <c r="AD6" s="73" t="s">
         <v>43</v>
       </c>
-      <c r="AE6" s="50"/>
-      <c r="AF6" s="50"/>
-      <c r="AG6" s="50"/>
+      <c r="AE6" s="73"/>
+      <c r="AF6" s="73"/>
+      <c r="AG6" s="73"/>
     </row>
     <row r="7" spans="1:63" ht="15.75">
       <c r="A7" s="5"/>
@@ -1525,7 +1526,7 @@
       <c r="AG7" s="13"/>
     </row>
     <row r="8" spans="1:63">
-      <c r="A8" s="56" t="s">
+      <c r="A8" s="60" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="19"/>
@@ -1592,7 +1593,7 @@
       <c r="BK8" s="2"/>
     </row>
     <row r="9" spans="1:63" ht="15.75">
-      <c r="A9" s="56"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
@@ -1661,7 +1662,7 @@
       <c r="BK9" s="2"/>
     </row>
     <row r="10" spans="1:63">
-      <c r="A10" s="56"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="26"/>
       <c r="C10" s="27"/>
       <c r="D10" s="28"/>
@@ -1726,7 +1727,7 @@
       <c r="BK10" s="2"/>
     </row>
     <row r="11" spans="1:63">
-      <c r="A11" s="56"/>
+      <c r="A11" s="60"/>
       <c r="B11" s="30"/>
       <c r="C11" s="31"/>
       <c r="D11" s="21"/>
@@ -1791,7 +1792,7 @@
       <c r="BK11" s="2"/>
     </row>
     <row r="12" spans="1:63" ht="15.75">
-      <c r="A12" s="56"/>
+      <c r="A12" s="60"/>
       <c r="B12" s="19" t="s">
         <v>9</v>
       </c>
@@ -1860,7 +1861,7 @@
       <c r="BK12" s="2"/>
     </row>
     <row r="13" spans="1:63">
-      <c r="A13" s="56"/>
+      <c r="A13" s="60"/>
       <c r="B13" s="26"/>
       <c r="C13" s="27"/>
       <c r="D13" s="28"/>
@@ -1925,7 +1926,7 @@
       <c r="BK13" s="2"/>
     </row>
     <row r="14" spans="1:63">
-      <c r="A14" s="56"/>
+      <c r="A14" s="60"/>
       <c r="B14" s="30"/>
       <c r="C14" s="31"/>
       <c r="D14" s="21"/>
@@ -1990,7 +1991,7 @@
       <c r="BK14" s="2"/>
     </row>
     <row r="15" spans="1:63" ht="15.75">
-      <c r="A15" s="56"/>
+      <c r="A15" s="60"/>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
@@ -2059,7 +2060,7 @@
       <c r="BK15" s="2"/>
     </row>
     <row r="16" spans="1:63">
-      <c r="A16" s="56"/>
+      <c r="A16" s="60"/>
       <c r="B16" s="26"/>
       <c r="C16" s="27"/>
       <c r="D16" s="28"/>
@@ -2124,7 +2125,7 @@
       <c r="BK16" s="2"/>
     </row>
     <row r="17" spans="1:63">
-      <c r="A17" s="56"/>
+      <c r="A17" s="60"/>
       <c r="B17" s="30"/>
       <c r="C17" s="31"/>
       <c r="D17" s="21"/>
@@ -2189,7 +2190,7 @@
       <c r="BK17" s="2"/>
     </row>
     <row r="18" spans="1:63" ht="15.75">
-      <c r="A18" s="56"/>
+      <c r="A18" s="60"/>
       <c r="B18" s="19" t="s">
         <v>13</v>
       </c>
@@ -2258,7 +2259,7 @@
       <c r="BK18" s="2"/>
     </row>
     <row r="19" spans="1:63">
-      <c r="A19" s="63"/>
+      <c r="A19" s="67"/>
       <c r="B19" s="26"/>
       <c r="C19" s="27"/>
       <c r="D19" s="28"/>
@@ -2440,7 +2441,7 @@
       <c r="BK20" s="2"/>
     </row>
     <row r="21" spans="1:63">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="59" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="30"/>
@@ -2507,7 +2508,7 @@
       <c r="BK21" s="2"/>
     </row>
     <row r="22" spans="1:63" ht="15.75">
-      <c r="A22" s="56"/>
+      <c r="A22" s="60"/>
       <c r="B22" s="19" t="s">
         <v>7</v>
       </c>
@@ -2576,7 +2577,7 @@
       <c r="BK22" s="2"/>
     </row>
     <row r="23" spans="1:63">
-      <c r="A23" s="56"/>
+      <c r="A23" s="60"/>
       <c r="B23" s="26"/>
       <c r="C23" s="27"/>
       <c r="D23" s="28"/>
@@ -2641,7 +2642,7 @@
       <c r="BK23" s="2"/>
     </row>
     <row r="24" spans="1:63">
-      <c r="A24" s="56"/>
+      <c r="A24" s="60"/>
       <c r="B24" s="30"/>
       <c r="C24" s="31"/>
       <c r="D24" s="21"/>
@@ -2706,7 +2707,7 @@
       <c r="BK24" s="2"/>
     </row>
     <row r="25" spans="1:63" ht="15.75">
-      <c r="A25" s="56"/>
+      <c r="A25" s="60"/>
       <c r="B25" s="19" t="s">
         <v>9</v>
       </c>
@@ -2775,7 +2776,7 @@
       <c r="BK25" s="2"/>
     </row>
     <row r="26" spans="1:63">
-      <c r="A26" s="56"/>
+      <c r="A26" s="60"/>
       <c r="B26" s="26"/>
       <c r="C26" s="27"/>
       <c r="D26" s="28"/>
@@ -2840,7 +2841,7 @@
       <c r="BK26" s="2"/>
     </row>
     <row r="27" spans="1:63">
-      <c r="A27" s="56"/>
+      <c r="A27" s="60"/>
       <c r="B27" s="30"/>
       <c r="C27" s="31"/>
       <c r="D27" s="21"/>
@@ -2905,7 +2906,7 @@
       <c r="BK27" s="2"/>
     </row>
     <row r="28" spans="1:63" ht="15.75">
-      <c r="A28" s="56"/>
+      <c r="A28" s="60"/>
       <c r="B28" s="19" t="s">
         <v>11</v>
       </c>
@@ -2974,7 +2975,7 @@
       <c r="BK28" s="2"/>
     </row>
     <row r="29" spans="1:63">
-      <c r="A29" s="56"/>
+      <c r="A29" s="60"/>
       <c r="B29" s="26"/>
       <c r="C29" s="27"/>
       <c r="D29" s="28"/>
@@ -3039,7 +3040,7 @@
       <c r="BK29" s="2"/>
     </row>
     <row r="30" spans="1:63">
-      <c r="A30" s="56"/>
+      <c r="A30" s="60"/>
       <c r="B30" s="30"/>
       <c r="C30" s="31"/>
       <c r="D30" s="21"/>
@@ -3104,7 +3105,7 @@
       <c r="BK30" s="2"/>
     </row>
     <row r="31" spans="1:63" ht="15.75">
-      <c r="A31" s="56"/>
+      <c r="A31" s="60"/>
       <c r="B31" s="19" t="s">
         <v>13</v>
       </c>
@@ -3173,7 +3174,7 @@
       <c r="BK31" s="2"/>
     </row>
     <row r="32" spans="1:63">
-      <c r="A32" s="63"/>
+      <c r="A32" s="67"/>
       <c r="B32" s="26"/>
       <c r="C32" s="27"/>
       <c r="D32" s="28"/>
@@ -3361,7 +3362,7 @@
       <c r="BK33" s="2"/>
     </row>
     <row r="34" spans="1:63">
-      <c r="A34" s="55" t="s">
+      <c r="A34" s="59" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="30"/>
@@ -3428,7 +3429,7 @@
       <c r="BK34" s="2"/>
     </row>
     <row r="35" spans="1:63" ht="15.75">
-      <c r="A35" s="56"/>
+      <c r="A35" s="60"/>
       <c r="B35" s="19" t="s">
         <v>7</v>
       </c>
@@ -3497,7 +3498,7 @@
       <c r="BK35" s="2"/>
     </row>
     <row r="36" spans="1:63">
-      <c r="A36" s="56"/>
+      <c r="A36" s="60"/>
       <c r="B36" s="26"/>
       <c r="C36" s="27"/>
       <c r="D36" s="28"/>
@@ -3562,7 +3563,7 @@
       <c r="BK36" s="2"/>
     </row>
     <row r="37" spans="1:63">
-      <c r="A37" s="56"/>
+      <c r="A37" s="60"/>
       <c r="B37" s="30"/>
       <c r="C37" s="31"/>
       <c r="D37" s="21"/>
@@ -3627,7 +3628,7 @@
       <c r="BK37" s="2"/>
     </row>
     <row r="38" spans="1:63" ht="15.75">
-      <c r="A38" s="56"/>
+      <c r="A38" s="60"/>
       <c r="B38" s="19" t="s">
         <v>9</v>
       </c>
@@ -3696,7 +3697,7 @@
       <c r="BK38" s="2"/>
     </row>
     <row r="39" spans="1:63">
-      <c r="A39" s="56"/>
+      <c r="A39" s="60"/>
       <c r="B39" s="26"/>
       <c r="C39" s="27"/>
       <c r="D39" s="28"/>
@@ -3761,7 +3762,7 @@
       <c r="BK39" s="2"/>
     </row>
     <row r="40" spans="1:63">
-      <c r="A40" s="56"/>
+      <c r="A40" s="60"/>
       <c r="B40" s="30"/>
       <c r="C40" s="31"/>
       <c r="D40" s="21"/>
@@ -3826,7 +3827,7 @@
       <c r="BK40" s="2"/>
     </row>
     <row r="41" spans="1:63" ht="15.75">
-      <c r="A41" s="56"/>
+      <c r="A41" s="60"/>
       <c r="B41" s="19" t="s">
         <v>11</v>
       </c>
@@ -3895,7 +3896,7 @@
       <c r="BK41" s="2"/>
     </row>
     <row r="42" spans="1:63">
-      <c r="A42" s="56"/>
+      <c r="A42" s="60"/>
       <c r="B42" s="26"/>
       <c r="C42" s="27"/>
       <c r="D42" s="28"/>
@@ -3960,7 +3961,7 @@
       <c r="BK42" s="2"/>
     </row>
     <row r="43" spans="1:63">
-      <c r="A43" s="56"/>
+      <c r="A43" s="60"/>
       <c r="B43" s="30"/>
       <c r="C43" s="31"/>
       <c r="D43" s="21"/>
@@ -4025,7 +4026,7 @@
       <c r="BK43" s="2"/>
     </row>
     <row r="44" spans="1:63" ht="15.75">
-      <c r="A44" s="56"/>
+      <c r="A44" s="60"/>
       <c r="B44" s="19" t="s">
         <v>13</v>
       </c>
@@ -4094,7 +4095,7 @@
       <c r="BK44" s="2"/>
     </row>
     <row r="45" spans="1:63">
-      <c r="A45" s="63"/>
+      <c r="A45" s="67"/>
       <c r="B45" s="26"/>
       <c r="C45" s="27"/>
       <c r="D45" s="28"/>
@@ -4282,7 +4283,7 @@
       <c r="BK46" s="2"/>
     </row>
     <row r="47" spans="1:63">
-      <c r="A47" s="55" t="s">
+      <c r="A47" s="59" t="s">
         <v>35</v>
       </c>
       <c r="B47" s="30"/>
@@ -4349,7 +4350,7 @@
       <c r="BK47" s="2"/>
     </row>
     <row r="48" spans="1:63" ht="15.75">
-      <c r="A48" s="56"/>
+      <c r="A48" s="60"/>
       <c r="B48" s="19" t="s">
         <v>7</v>
       </c>
@@ -4418,7 +4419,7 @@
       <c r="BK48" s="2"/>
     </row>
     <row r="49" spans="1:63">
-      <c r="A49" s="56"/>
+      <c r="A49" s="60"/>
       <c r="B49" s="26"/>
       <c r="C49" s="27"/>
       <c r="D49" s="28"/>
@@ -4483,7 +4484,7 @@
       <c r="BK49" s="2"/>
     </row>
     <row r="50" spans="1:63">
-      <c r="A50" s="56"/>
+      <c r="A50" s="60"/>
       <c r="B50" s="30"/>
       <c r="C50" s="31"/>
       <c r="D50" s="21"/>
@@ -4548,7 +4549,7 @@
       <c r="BK50" s="2"/>
     </row>
     <row r="51" spans="1:63" ht="15.75">
-      <c r="A51" s="56"/>
+      <c r="A51" s="60"/>
       <c r="B51" s="19" t="s">
         <v>9</v>
       </c>
@@ -4617,7 +4618,7 @@
       <c r="BK51" s="2"/>
     </row>
     <row r="52" spans="1:63">
-      <c r="A52" s="56"/>
+      <c r="A52" s="60"/>
       <c r="B52" s="26"/>
       <c r="C52" s="27"/>
       <c r="D52" s="28"/>
@@ -4682,7 +4683,7 @@
       <c r="BK52" s="2"/>
     </row>
     <row r="53" spans="1:63">
-      <c r="A53" s="56"/>
+      <c r="A53" s="60"/>
       <c r="B53" s="30"/>
       <c r="C53" s="31"/>
       <c r="D53" s="21"/>
@@ -4747,7 +4748,7 @@
       <c r="BK53" s="2"/>
     </row>
     <row r="54" spans="1:63" ht="15.75">
-      <c r="A54" s="56"/>
+      <c r="A54" s="60"/>
       <c r="B54" s="19" t="s">
         <v>11</v>
       </c>
@@ -4816,7 +4817,7 @@
       <c r="BK54" s="2"/>
     </row>
     <row r="55" spans="1:63">
-      <c r="A55" s="56"/>
+      <c r="A55" s="60"/>
       <c r="B55" s="26"/>
       <c r="C55" s="27"/>
       <c r="D55" s="28"/>
@@ -4881,7 +4882,7 @@
       <c r="BK55" s="2"/>
     </row>
     <row r="56" spans="1:63">
-      <c r="A56" s="56"/>
+      <c r="A56" s="60"/>
       <c r="B56" s="30"/>
       <c r="C56" s="31"/>
       <c r="D56" s="21"/>
@@ -4946,7 +4947,7 @@
       <c r="BK56" s="2"/>
     </row>
     <row r="57" spans="1:63" ht="15.75">
-      <c r="A57" s="56"/>
+      <c r="A57" s="60"/>
       <c r="B57" s="19" t="s">
         <v>13</v>
       </c>
@@ -5015,7 +5016,7 @@
       <c r="BK57" s="2"/>
     </row>
     <row r="58" spans="1:63">
-      <c r="A58" s="63"/>
+      <c r="A58" s="67"/>
       <c r="B58" s="26"/>
       <c r="C58" s="27"/>
       <c r="D58" s="28"/>
@@ -5205,7 +5206,7 @@
       <c r="BK59" s="2"/>
     </row>
     <row r="60" spans="1:63">
-      <c r="A60" s="55" t="s">
+      <c r="A60" s="59" t="s">
         <v>36</v>
       </c>
       <c r="B60" s="30"/>
@@ -5272,7 +5273,7 @@
       <c r="BK60" s="2"/>
     </row>
     <row r="61" spans="1:63" ht="15.75">
-      <c r="A61" s="56"/>
+      <c r="A61" s="60"/>
       <c r="B61" s="19" t="s">
         <v>7</v>
       </c>
@@ -5341,7 +5342,7 @@
       <c r="BK61" s="2"/>
     </row>
     <row r="62" spans="1:63">
-      <c r="A62" s="56"/>
+      <c r="A62" s="60"/>
       <c r="B62" s="26"/>
       <c r="C62" s="27"/>
       <c r="D62" s="28"/>
@@ -5406,7 +5407,7 @@
       <c r="BK62" s="2"/>
     </row>
     <row r="63" spans="1:63">
-      <c r="A63" s="56"/>
+      <c r="A63" s="60"/>
       <c r="B63" s="30"/>
       <c r="C63" s="31"/>
       <c r="D63" s="21"/>
@@ -5471,7 +5472,7 @@
       <c r="BK63" s="2"/>
     </row>
     <row r="64" spans="1:63" ht="15.75">
-      <c r="A64" s="56"/>
+      <c r="A64" s="60"/>
       <c r="B64" s="19" t="s">
         <v>9</v>
       </c>
@@ -5540,7 +5541,7 @@
       <c r="BK64" s="2"/>
     </row>
     <row r="65" spans="1:63">
-      <c r="A65" s="56"/>
+      <c r="A65" s="60"/>
       <c r="B65" s="26"/>
       <c r="C65" s="27"/>
       <c r="D65" s="28"/>
@@ -5605,7 +5606,7 @@
       <c r="BK65" s="2"/>
     </row>
     <row r="66" spans="1:63">
-      <c r="A66" s="56"/>
+      <c r="A66" s="60"/>
       <c r="B66" s="30"/>
       <c r="C66" s="31"/>
       <c r="D66" s="21"/>
@@ -5670,7 +5671,7 @@
       <c r="BK66" s="2"/>
     </row>
     <row r="67" spans="1:63" ht="15.75">
-      <c r="A67" s="56"/>
+      <c r="A67" s="60"/>
       <c r="B67" s="19" t="s">
         <v>11</v>
       </c>
@@ -5739,7 +5740,7 @@
       <c r="BK67" s="2"/>
     </row>
     <row r="68" spans="1:63">
-      <c r="A68" s="56"/>
+      <c r="A68" s="60"/>
       <c r="B68" s="26"/>
       <c r="C68" s="27"/>
       <c r="D68" s="28"/>
@@ -5804,7 +5805,7 @@
       <c r="BK68" s="2"/>
     </row>
     <row r="69" spans="1:63">
-      <c r="A69" s="56"/>
+      <c r="A69" s="60"/>
       <c r="B69" s="30"/>
       <c r="C69" s="31"/>
       <c r="D69" s="21"/>
@@ -5869,7 +5870,7 @@
       <c r="BK69" s="2"/>
     </row>
     <row r="70" spans="1:63" ht="15.75">
-      <c r="A70" s="56"/>
+      <c r="A70" s="60"/>
       <c r="B70" s="19" t="s">
         <v>13</v>
       </c>
@@ -5938,7 +5939,7 @@
       <c r="BK70" s="2"/>
     </row>
     <row r="71" spans="1:63">
-      <c r="A71" s="63"/>
+      <c r="A71" s="67"/>
       <c r="B71" s="26"/>
       <c r="C71" s="27"/>
       <c r="D71" s="28"/>
@@ -6128,7 +6129,7 @@
       <c r="BK72" s="2"/>
     </row>
     <row r="73" spans="1:63">
-      <c r="A73" s="55" t="s">
+      <c r="A73" s="59" t="s">
         <v>37</v>
       </c>
       <c r="B73" s="30"/>
@@ -6195,7 +6196,7 @@
       <c r="BK73" s="2"/>
     </row>
     <row r="74" spans="1:63" ht="15.75">
-      <c r="A74" s="56"/>
+      <c r="A74" s="60"/>
       <c r="B74" s="19" t="s">
         <v>7</v>
       </c>
@@ -6264,7 +6265,7 @@
       <c r="BK74" s="2"/>
     </row>
     <row r="75" spans="1:63">
-      <c r="A75" s="56"/>
+      <c r="A75" s="60"/>
       <c r="B75" s="26"/>
       <c r="C75" s="27"/>
       <c r="D75" s="28"/>
@@ -6329,7 +6330,7 @@
       <c r="BK75" s="2"/>
     </row>
     <row r="76" spans="1:63">
-      <c r="A76" s="56"/>
+      <c r="A76" s="60"/>
       <c r="B76" s="30"/>
       <c r="C76" s="31"/>
       <c r="D76" s="21"/>
@@ -6394,7 +6395,7 @@
       <c r="BK76" s="2"/>
     </row>
     <row r="77" spans="1:63" ht="15.75">
-      <c r="A77" s="56"/>
+      <c r="A77" s="60"/>
       <c r="B77" s="19" t="s">
         <v>9</v>
       </c>
@@ -6463,7 +6464,7 @@
       <c r="BK77" s="2"/>
     </row>
     <row r="78" spans="1:63">
-      <c r="A78" s="56"/>
+      <c r="A78" s="60"/>
       <c r="B78" s="26"/>
       <c r="C78" s="27"/>
       <c r="D78" s="28"/>
@@ -6528,7 +6529,7 @@
       <c r="BK78" s="2"/>
     </row>
     <row r="79" spans="1:63">
-      <c r="A79" s="56"/>
+      <c r="A79" s="60"/>
       <c r="B79" s="30"/>
       <c r="C79" s="31"/>
       <c r="D79" s="21"/>
@@ -6593,7 +6594,7 @@
       <c r="BK79" s="2"/>
     </row>
     <row r="80" spans="1:63" ht="15.75">
-      <c r="A80" s="56"/>
+      <c r="A80" s="60"/>
       <c r="B80" s="19" t="s">
         <v>11</v>
       </c>
@@ -6662,7 +6663,7 @@
       <c r="BK80" s="2"/>
     </row>
     <row r="81" spans="1:63">
-      <c r="A81" s="57"/>
+      <c r="A81" s="61"/>
       <c r="B81" s="26"/>
       <c r="C81" s="27"/>
       <c r="D81" s="28"/>
@@ -6746,12 +6747,12 @@
       <c r="R82" s="10"/>
       <c r="S82" s="10"/>
       <c r="T82" s="10"/>
-      <c r="U82" s="71"/>
-      <c r="V82" s="71"/>
-      <c r="W82" s="71"/>
-      <c r="X82" s="71"/>
-      <c r="Y82" s="71"/>
-      <c r="Z82" s="71"/>
+      <c r="U82" s="57"/>
+      <c r="V82" s="57"/>
+      <c r="W82" s="57"/>
+      <c r="X82" s="57"/>
+      <c r="Y82" s="57"/>
+      <c r="Z82" s="57"/>
       <c r="AA82" s="10"/>
       <c r="AB82" s="10"/>
       <c r="AC82" s="10"/>
@@ -6770,48 +6771,48 @@
       <c r="BI82" s="2"/>
     </row>
     <row r="83" spans="1:63" ht="15" customHeight="1">
-      <c r="A83" s="54" t="s">
+      <c r="A83" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B83" s="64" t="s">
+      <c r="B83" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="C83" s="64"/>
-      <c r="D83" s="64"/>
-      <c r="E83" s="64"/>
-      <c r="F83" s="64"/>
-      <c r="G83" s="64"/>
-      <c r="H83" s="64"/>
-      <c r="I83" s="65" t="s">
+      <c r="C83" s="68"/>
+      <c r="D83" s="68"/>
+      <c r="E83" s="68"/>
+      <c r="F83" s="68"/>
+      <c r="G83" s="68"/>
+      <c r="H83" s="68"/>
+      <c r="I83" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="J83" s="66" t="s">
+      <c r="J83" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="K83" s="66"/>
-      <c r="L83" s="66"/>
-      <c r="M83" s="66"/>
-      <c r="N83" s="66" t="s">
+      <c r="K83" s="52"/>
+      <c r="L83" s="52"/>
+      <c r="M83" s="52"/>
+      <c r="N83" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="O83" s="66"/>
-      <c r="P83" s="66"/>
-      <c r="Q83" s="66"/>
-      <c r="R83" s="72" t="s">
+      <c r="O83" s="52"/>
+      <c r="P83" s="52"/>
+      <c r="Q83" s="52"/>
+      <c r="R83" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="S83" s="65" t="s">
+      <c r="S83" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="T83" s="72" t="s">
+      <c r="T83" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="U83" s="72"/>
-      <c r="V83" s="65" t="s">
+      <c r="U83" s="50"/>
+      <c r="V83" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="W83" s="65"/>
-      <c r="X83" s="65"/>
+      <c r="W83" s="51"/>
+      <c r="X83" s="51"/>
       <c r="Y83" s="10"/>
       <c r="Z83" s="10"/>
       <c r="AA83" s="10"/>
@@ -6823,34 +6824,34 @@
       <c r="AG83" s="10"/>
     </row>
     <row r="84" spans="1:63">
-      <c r="A84" s="54"/>
-      <c r="B84" s="64"/>
-      <c r="C84" s="64"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="64"/>
-      <c r="F84" s="64"/>
-      <c r="G84" s="64"/>
-      <c r="H84" s="64"/>
-      <c r="I84" s="65"/>
-      <c r="J84" s="67" t="s">
+      <c r="A84" s="58"/>
+      <c r="B84" s="68"/>
+      <c r="C84" s="68"/>
+      <c r="D84" s="68"/>
+      <c r="E84" s="68"/>
+      <c r="F84" s="68"/>
+      <c r="G84" s="68"/>
+      <c r="H84" s="68"/>
+      <c r="I84" s="51"/>
+      <c r="J84" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="K84" s="67"/>
-      <c r="L84" s="67"/>
-      <c r="M84" s="67"/>
-      <c r="N84" s="66"/>
-      <c r="O84" s="66"/>
-      <c r="P84" s="66"/>
-      <c r="Q84" s="66"/>
-      <c r="R84" s="72"/>
-      <c r="S84" s="65"/>
-      <c r="T84" s="72"/>
-      <c r="U84" s="72"/>
-      <c r="V84" s="65" t="s">
+      <c r="K84" s="72"/>
+      <c r="L84" s="72"/>
+      <c r="M84" s="72"/>
+      <c r="N84" s="52"/>
+      <c r="O84" s="52"/>
+      <c r="P84" s="52"/>
+      <c r="Q84" s="52"/>
+      <c r="R84" s="50"/>
+      <c r="S84" s="51"/>
+      <c r="T84" s="50"/>
+      <c r="U84" s="50"/>
+      <c r="V84" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="W84" s="65"/>
-      <c r="X84" s="65"/>
+      <c r="W84" s="51"/>
+      <c r="X84" s="51"/>
       <c r="Y84" s="10"/>
       <c r="Z84" s="10"/>
       <c r="AA84" s="10"/>
@@ -6862,27 +6863,27 @@
       <c r="AG84" s="10"/>
     </row>
     <row r="85" spans="1:63">
-      <c r="A85" s="54"/>
-      <c r="B85" s="64"/>
-      <c r="C85" s="64"/>
-      <c r="D85" s="64"/>
-      <c r="E85" s="64"/>
-      <c r="F85" s="64"/>
-      <c r="G85" s="64"/>
-      <c r="H85" s="64"/>
-      <c r="I85" s="65"/>
-      <c r="J85" s="67"/>
-      <c r="K85" s="67"/>
-      <c r="L85" s="67"/>
-      <c r="M85" s="67"/>
-      <c r="N85" s="66"/>
-      <c r="O85" s="66"/>
-      <c r="P85" s="66"/>
-      <c r="Q85" s="66"/>
-      <c r="R85" s="72"/>
-      <c r="S85" s="65"/>
-      <c r="T85" s="72"/>
-      <c r="U85" s="72"/>
+      <c r="A85" s="58"/>
+      <c r="B85" s="68"/>
+      <c r="C85" s="68"/>
+      <c r="D85" s="68"/>
+      <c r="E85" s="68"/>
+      <c r="F85" s="68"/>
+      <c r="G85" s="68"/>
+      <c r="H85" s="68"/>
+      <c r="I85" s="51"/>
+      <c r="J85" s="72"/>
+      <c r="K85" s="72"/>
+      <c r="L85" s="72"/>
+      <c r="M85" s="72"/>
+      <c r="N85" s="52"/>
+      <c r="O85" s="52"/>
+      <c r="P85" s="52"/>
+      <c r="Q85" s="52"/>
+      <c r="R85" s="50"/>
+      <c r="S85" s="51"/>
+      <c r="T85" s="50"/>
+      <c r="U85" s="50"/>
       <c r="V85" s="43" t="s">
         <v>26</v>
       </c>
@@ -6904,26 +6905,26 @@
     </row>
     <row r="86" spans="1:63" ht="15" customHeight="1">
       <c r="A86" s="7"/>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68"/>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
-      <c r="H86" s="68"/>
+      <c r="B86" s="54"/>
+      <c r="C86" s="54"/>
+      <c r="D86" s="54"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="54"/>
+      <c r="H86" s="54"/>
       <c r="I86" s="44"/>
-      <c r="J86" s="73"/>
-      <c r="K86" s="73"/>
-      <c r="L86" s="73"/>
-      <c r="M86" s="73"/>
-      <c r="N86" s="69"/>
-      <c r="O86" s="69"/>
-      <c r="P86" s="69"/>
-      <c r="Q86" s="69"/>
+      <c r="J86" s="55"/>
+      <c r="K86" s="55"/>
+      <c r="L86" s="55"/>
+      <c r="M86" s="55"/>
+      <c r="N86" s="53"/>
+      <c r="O86" s="53"/>
+      <c r="P86" s="53"/>
+      <c r="Q86" s="53"/>
       <c r="R86" s="44"/>
       <c r="S86" s="45"/>
-      <c r="T86" s="70"/>
-      <c r="U86" s="70"/>
+      <c r="T86" s="56"/>
+      <c r="U86" s="56"/>
       <c r="V86" s="46"/>
       <c r="W86" s="46"/>
       <c r="X86" s="47"/>
@@ -6969,26 +6970,26 @@
     </row>
     <row r="87" spans="1:63" ht="46.5" customHeight="1">
       <c r="A87" s="8"/>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68"/>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="68"/>
+      <c r="B87" s="54"/>
+      <c r="C87" s="54"/>
+      <c r="D87" s="54"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="54"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="54"/>
       <c r="I87" s="44"/>
-      <c r="J87" s="69"/>
-      <c r="K87" s="69"/>
-      <c r="L87" s="69"/>
-      <c r="M87" s="69"/>
-      <c r="N87" s="69"/>
-      <c r="O87" s="69"/>
-      <c r="P87" s="69"/>
-      <c r="Q87" s="69"/>
+      <c r="J87" s="53"/>
+      <c r="K87" s="53"/>
+      <c r="L87" s="53"/>
+      <c r="M87" s="53"/>
+      <c r="N87" s="53"/>
+      <c r="O87" s="53"/>
+      <c r="P87" s="53"/>
+      <c r="Q87" s="53"/>
       <c r="R87" s="44"/>
       <c r="S87" s="45"/>
-      <c r="T87" s="70"/>
-      <c r="U87" s="70"/>
+      <c r="T87" s="56"/>
+      <c r="U87" s="56"/>
       <c r="V87" s="46"/>
       <c r="W87" s="46"/>
       <c r="X87" s="47"/>
@@ -7034,26 +7035,26 @@
     </row>
     <row r="88" spans="1:63" ht="45.75" customHeight="1">
       <c r="A88" s="8"/>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68"/>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
-      <c r="H88" s="68"/>
+      <c r="B88" s="54"/>
+      <c r="C88" s="54"/>
+      <c r="D88" s="54"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="54"/>
+      <c r="G88" s="54"/>
+      <c r="H88" s="54"/>
       <c r="I88" s="44"/>
-      <c r="J88" s="69"/>
-      <c r="K88" s="69"/>
-      <c r="L88" s="69"/>
-      <c r="M88" s="69"/>
-      <c r="N88" s="69"/>
-      <c r="O88" s="69"/>
-      <c r="P88" s="69"/>
-      <c r="Q88" s="69"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="53"/>
+      <c r="L88" s="53"/>
+      <c r="M88" s="53"/>
+      <c r="N88" s="53"/>
+      <c r="O88" s="53"/>
+      <c r="P88" s="53"/>
+      <c r="Q88" s="53"/>
       <c r="R88" s="44"/>
       <c r="S88" s="45"/>
-      <c r="T88" s="70"/>
-      <c r="U88" s="70"/>
+      <c r="T88" s="56"/>
+      <c r="U88" s="56"/>
       <c r="V88" s="46"/>
       <c r="W88" s="46"/>
       <c r="X88" s="47"/>
@@ -7099,26 +7100,26 @@
     </row>
     <row r="89" spans="1:63" ht="42" customHeight="1">
       <c r="A89" s="8"/>
-      <c r="B89" s="68"/>
-      <c r="C89" s="68"/>
-      <c r="D89" s="68"/>
-      <c r="E89" s="68"/>
-      <c r="F89" s="68"/>
-      <c r="G89" s="68"/>
-      <c r="H89" s="68"/>
+      <c r="B89" s="54"/>
+      <c r="C89" s="54"/>
+      <c r="D89" s="54"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="54"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="54"/>
       <c r="I89" s="44"/>
-      <c r="J89" s="69"/>
-      <c r="K89" s="69"/>
-      <c r="L89" s="69"/>
-      <c r="M89" s="69"/>
-      <c r="N89" s="69"/>
-      <c r="O89" s="69"/>
-      <c r="P89" s="69"/>
-      <c r="Q89" s="69"/>
+      <c r="J89" s="53"/>
+      <c r="K89" s="53"/>
+      <c r="L89" s="53"/>
+      <c r="M89" s="53"/>
+      <c r="N89" s="53"/>
+      <c r="O89" s="53"/>
+      <c r="P89" s="53"/>
+      <c r="Q89" s="53"/>
       <c r="R89" s="44"/>
       <c r="S89" s="45"/>
-      <c r="T89" s="70"/>
-      <c r="U89" s="70"/>
+      <c r="T89" s="56"/>
+      <c r="U89" s="56"/>
       <c r="V89" s="46"/>
       <c r="W89" s="46"/>
       <c r="X89" s="47"/>
@@ -7164,26 +7165,26 @@
     </row>
     <row r="90" spans="1:63" ht="27" customHeight="1">
       <c r="A90" s="9"/>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68"/>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
-      <c r="H90" s="68"/>
+      <c r="B90" s="54"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="54"/>
+      <c r="E90" s="54"/>
+      <c r="F90" s="54"/>
+      <c r="G90" s="54"/>
+      <c r="H90" s="54"/>
       <c r="I90" s="44"/>
-      <c r="J90" s="69"/>
-      <c r="K90" s="69"/>
-      <c r="L90" s="69"/>
-      <c r="M90" s="69"/>
-      <c r="N90" s="69"/>
-      <c r="O90" s="69"/>
-      <c r="P90" s="69"/>
-      <c r="Q90" s="69"/>
+      <c r="J90" s="53"/>
+      <c r="K90" s="53"/>
+      <c r="L90" s="53"/>
+      <c r="M90" s="53"/>
+      <c r="N90" s="53"/>
+      <c r="O90" s="53"/>
+      <c r="P90" s="53"/>
+      <c r="Q90" s="53"/>
       <c r="R90" s="44"/>
       <c r="S90" s="45"/>
-      <c r="T90" s="70"/>
-      <c r="U90" s="70"/>
+      <c r="T90" s="56"/>
+      <c r="U90" s="56"/>
       <c r="V90" s="46"/>
       <c r="W90" s="46"/>
       <c r="X90" s="47"/>
@@ -7229,26 +7230,26 @@
     </row>
     <row r="91" spans="1:63" ht="45.75" customHeight="1">
       <c r="A91" s="8"/>
-      <c r="B91" s="68"/>
-      <c r="C91" s="68"/>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
-      <c r="H91" s="68"/>
+      <c r="B91" s="54"/>
+      <c r="C91" s="54"/>
+      <c r="D91" s="54"/>
+      <c r="E91" s="54"/>
+      <c r="F91" s="54"/>
+      <c r="G91" s="54"/>
+      <c r="H91" s="54"/>
       <c r="I91" s="44"/>
-      <c r="J91" s="69"/>
-      <c r="K91" s="69"/>
-      <c r="L91" s="69"/>
-      <c r="M91" s="69"/>
-      <c r="N91" s="69"/>
-      <c r="O91" s="69"/>
-      <c r="P91" s="69"/>
-      <c r="Q91" s="69"/>
+      <c r="J91" s="53"/>
+      <c r="K91" s="53"/>
+      <c r="L91" s="53"/>
+      <c r="M91" s="53"/>
+      <c r="N91" s="53"/>
+      <c r="O91" s="53"/>
+      <c r="P91" s="53"/>
+      <c r="Q91" s="53"/>
       <c r="R91" s="44"/>
       <c r="S91" s="45"/>
-      <c r="T91" s="70"/>
-      <c r="U91" s="70"/>
+      <c r="T91" s="56"/>
+      <c r="U91" s="56"/>
       <c r="V91" s="46"/>
       <c r="W91" s="46"/>
       <c r="X91" s="47"/>
@@ -7294,26 +7295,26 @@
     </row>
     <row r="92" spans="1:63" ht="15" customHeight="1">
       <c r="A92" s="8"/>
-      <c r="B92" s="68"/>
-      <c r="C92" s="68"/>
-      <c r="D92" s="68"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="68"/>
-      <c r="H92" s="68"/>
+      <c r="B92" s="54"/>
+      <c r="C92" s="54"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="54"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="54"/>
+      <c r="H92" s="54"/>
       <c r="I92" s="44"/>
-      <c r="J92" s="69"/>
-      <c r="K92" s="69"/>
-      <c r="L92" s="69"/>
-      <c r="M92" s="69"/>
-      <c r="N92" s="69"/>
-      <c r="O92" s="69"/>
-      <c r="P92" s="69"/>
-      <c r="Q92" s="69"/>
+      <c r="J92" s="53"/>
+      <c r="K92" s="53"/>
+      <c r="L92" s="53"/>
+      <c r="M92" s="53"/>
+      <c r="N92" s="53"/>
+      <c r="O92" s="53"/>
+      <c r="P92" s="53"/>
+      <c r="Q92" s="53"/>
       <c r="R92" s="44"/>
       <c r="S92" s="45"/>
-      <c r="T92" s="70"/>
-      <c r="U92" s="70"/>
+      <c r="T92" s="56"/>
+      <c r="U92" s="56"/>
       <c r="V92" s="46"/>
       <c r="W92" s="46"/>
       <c r="X92" s="47"/>
@@ -7359,26 +7360,26 @@
     </row>
     <row r="93" spans="1:63" ht="38.25" customHeight="1">
       <c r="A93" s="9"/>
-      <c r="B93" s="68"/>
-      <c r="C93" s="68"/>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
-      <c r="H93" s="68"/>
+      <c r="B93" s="54"/>
+      <c r="C93" s="54"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="54"/>
+      <c r="H93" s="54"/>
       <c r="I93" s="44"/>
-      <c r="J93" s="69"/>
-      <c r="K93" s="69"/>
-      <c r="L93" s="69"/>
-      <c r="M93" s="69"/>
-      <c r="N93" s="69"/>
-      <c r="O93" s="69"/>
-      <c r="P93" s="69"/>
-      <c r="Q93" s="69"/>
+      <c r="J93" s="53"/>
+      <c r="K93" s="53"/>
+      <c r="L93" s="53"/>
+      <c r="M93" s="53"/>
+      <c r="N93" s="53"/>
+      <c r="O93" s="53"/>
+      <c r="P93" s="53"/>
+      <c r="Q93" s="53"/>
       <c r="R93" s="44"/>
       <c r="S93" s="45"/>
-      <c r="T93" s="70"/>
-      <c r="U93" s="70"/>
+      <c r="T93" s="56"/>
+      <c r="U93" s="56"/>
       <c r="V93" s="46"/>
       <c r="W93" s="46"/>
       <c r="X93" s="47"/>
@@ -7424,26 +7425,26 @@
     </row>
     <row r="94" spans="1:63" ht="15" customHeight="1">
       <c r="A94" s="9"/>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68"/>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
-      <c r="H94" s="68"/>
+      <c r="B94" s="54"/>
+      <c r="C94" s="54"/>
+      <c r="D94" s="54"/>
+      <c r="E94" s="54"/>
+      <c r="F94" s="54"/>
+      <c r="G94" s="54"/>
+      <c r="H94" s="54"/>
       <c r="I94" s="44"/>
-      <c r="J94" s="69"/>
-      <c r="K94" s="69"/>
-      <c r="L94" s="69"/>
-      <c r="M94" s="69"/>
-      <c r="N94" s="69"/>
-      <c r="O94" s="69"/>
-      <c r="P94" s="69"/>
-      <c r="Q94" s="69"/>
+      <c r="J94" s="53"/>
+      <c r="K94" s="53"/>
+      <c r="L94" s="53"/>
+      <c r="M94" s="53"/>
+      <c r="N94" s="53"/>
+      <c r="O94" s="53"/>
+      <c r="P94" s="53"/>
+      <c r="Q94" s="53"/>
       <c r="R94" s="44"/>
       <c r="S94" s="45"/>
-      <c r="T94" s="70"/>
-      <c r="U94" s="70"/>
+      <c r="T94" s="56"/>
+      <c r="U94" s="56"/>
       <c r="V94" s="46"/>
       <c r="W94" s="46"/>
       <c r="X94" s="47"/>
@@ -7489,26 +7490,26 @@
     </row>
     <row r="95" spans="1:63" ht="42" customHeight="1">
       <c r="A95" s="9"/>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68"/>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
-      <c r="H95" s="68"/>
+      <c r="B95" s="54"/>
+      <c r="C95" s="54"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="54"/>
+      <c r="F95" s="54"/>
+      <c r="G95" s="54"/>
+      <c r="H95" s="54"/>
       <c r="I95" s="44"/>
-      <c r="J95" s="69"/>
-      <c r="K95" s="69"/>
-      <c r="L95" s="69"/>
-      <c r="M95" s="69"/>
-      <c r="N95" s="69"/>
-      <c r="O95" s="69"/>
-      <c r="P95" s="69"/>
-      <c r="Q95" s="69"/>
+      <c r="J95" s="53"/>
+      <c r="K95" s="53"/>
+      <c r="L95" s="53"/>
+      <c r="M95" s="53"/>
+      <c r="N95" s="53"/>
+      <c r="O95" s="53"/>
+      <c r="P95" s="53"/>
+      <c r="Q95" s="53"/>
       <c r="R95" s="44"/>
       <c r="S95" s="45"/>
-      <c r="T95" s="70"/>
-      <c r="U95" s="70"/>
+      <c r="T95" s="56"/>
+      <c r="U95" s="56"/>
       <c r="V95" s="46"/>
       <c r="W95" s="49"/>
       <c r="X95" s="47"/>
@@ -7554,26 +7555,26 @@
     </row>
     <row r="96" spans="1:63" ht="45" customHeight="1">
       <c r="A96" s="9"/>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68"/>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
-      <c r="H96" s="68"/>
+      <c r="B96" s="54"/>
+      <c r="C96" s="54"/>
+      <c r="D96" s="54"/>
+      <c r="E96" s="54"/>
+      <c r="F96" s="54"/>
+      <c r="G96" s="54"/>
+      <c r="H96" s="54"/>
       <c r="I96" s="44"/>
-      <c r="J96" s="69"/>
-      <c r="K96" s="69"/>
-      <c r="L96" s="69"/>
-      <c r="M96" s="69"/>
-      <c r="N96" s="69"/>
-      <c r="O96" s="69"/>
-      <c r="P96" s="69"/>
-      <c r="Q96" s="69"/>
+      <c r="J96" s="53"/>
+      <c r="K96" s="53"/>
+      <c r="L96" s="53"/>
+      <c r="M96" s="53"/>
+      <c r="N96" s="53"/>
+      <c r="O96" s="53"/>
+      <c r="P96" s="53"/>
+      <c r="Q96" s="53"/>
       <c r="R96" s="44"/>
       <c r="S96" s="45"/>
-      <c r="T96" s="70"/>
-      <c r="U96" s="70"/>
+      <c r="T96" s="56"/>
+      <c r="U96" s="56"/>
       <c r="V96" s="46"/>
       <c r="W96" s="46"/>
       <c r="X96" s="47"/>
@@ -7617,59 +7618,35 @@
       <c r="BJ96" s="3"/>
       <c r="BK96" s="3"/>
     </row>
+    <row r="97" s="74" customFormat="1"/>
+    <row r="98" s="74" customFormat="1"/>
+    <row r="99" s="74" customFormat="1"/>
+    <row r="100" s="74" customFormat="1"/>
+    <row r="101" s="74" customFormat="1"/>
+    <row r="102" s="74" customFormat="1"/>
+    <row r="103" s="74" customFormat="1"/>
+    <row r="104" s="74" customFormat="1"/>
+    <row r="105" s="74" customFormat="1"/>
+    <row r="106" s="74" customFormat="1"/>
+    <row r="107" s="74" customFormat="1"/>
+    <row r="108" s="74" customFormat="1"/>
+    <row r="109" s="74" customFormat="1"/>
+    <row r="110" s="74" customFormat="1"/>
+    <row r="111" s="74" customFormat="1"/>
+    <row r="112" s="74" customFormat="1"/>
+    <row r="113" s="74" customFormat="1"/>
+    <row r="114" s="74" customFormat="1"/>
+    <row r="115" s="74" customFormat="1"/>
+    <row r="116" s="74" customFormat="1"/>
+    <row r="117" s="74" customFormat="1"/>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="R83:R85"/>
-    <mergeCell ref="S83:S85"/>
-    <mergeCell ref="N83:Q85"/>
-    <mergeCell ref="N86:Q86"/>
-    <mergeCell ref="N87:Q87"/>
-    <mergeCell ref="B86:H86"/>
-    <mergeCell ref="B87:H87"/>
-    <mergeCell ref="B88:H88"/>
-    <mergeCell ref="B89:H89"/>
-    <mergeCell ref="N88:Q88"/>
-    <mergeCell ref="N89:Q89"/>
-    <mergeCell ref="J86:M86"/>
-    <mergeCell ref="J87:M87"/>
-    <mergeCell ref="T93:U93"/>
-    <mergeCell ref="T94:U94"/>
-    <mergeCell ref="T95:U95"/>
-    <mergeCell ref="T96:U96"/>
-    <mergeCell ref="T90:U90"/>
-    <mergeCell ref="T91:U91"/>
-    <mergeCell ref="T92:U92"/>
-    <mergeCell ref="T87:U87"/>
-    <mergeCell ref="T88:U88"/>
-    <mergeCell ref="T89:U89"/>
-    <mergeCell ref="V83:X83"/>
-    <mergeCell ref="U82:Z82"/>
-    <mergeCell ref="V84:X84"/>
-    <mergeCell ref="T86:U86"/>
-    <mergeCell ref="T83:U85"/>
-    <mergeCell ref="B93:H93"/>
-    <mergeCell ref="B94:H94"/>
-    <mergeCell ref="J93:M93"/>
-    <mergeCell ref="J94:M94"/>
-    <mergeCell ref="N93:Q93"/>
-    <mergeCell ref="N94:Q94"/>
-    <mergeCell ref="B95:H95"/>
-    <mergeCell ref="B96:H96"/>
-    <mergeCell ref="J95:M95"/>
-    <mergeCell ref="J96:M96"/>
-    <mergeCell ref="N95:Q95"/>
-    <mergeCell ref="N96:Q96"/>
-    <mergeCell ref="B91:H91"/>
-    <mergeCell ref="B92:H92"/>
-    <mergeCell ref="J91:M91"/>
-    <mergeCell ref="J92:M92"/>
-    <mergeCell ref="N91:Q91"/>
-    <mergeCell ref="N92:Q92"/>
-    <mergeCell ref="B90:H90"/>
-    <mergeCell ref="J89:M89"/>
-    <mergeCell ref="J90:M90"/>
-    <mergeCell ref="N90:Q90"/>
-    <mergeCell ref="J88:M88"/>
+    <mergeCell ref="AD6:AG6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="U6:X6"/>
     <mergeCell ref="A83:A85"/>
     <mergeCell ref="A73:A81"/>
     <mergeCell ref="N2:O2"/>
@@ -7686,12 +7663,57 @@
     <mergeCell ref="I83:I85"/>
     <mergeCell ref="J83:M83"/>
     <mergeCell ref="J84:M85"/>
-    <mergeCell ref="AD6:AG6"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="L6:P6"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="U6:X6"/>
+    <mergeCell ref="B90:H90"/>
+    <mergeCell ref="J89:M89"/>
+    <mergeCell ref="J90:M90"/>
+    <mergeCell ref="N90:Q90"/>
+    <mergeCell ref="J88:M88"/>
+    <mergeCell ref="B91:H91"/>
+    <mergeCell ref="B92:H92"/>
+    <mergeCell ref="J91:M91"/>
+    <mergeCell ref="J92:M92"/>
+    <mergeCell ref="N91:Q91"/>
+    <mergeCell ref="N92:Q92"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="B96:H96"/>
+    <mergeCell ref="J95:M95"/>
+    <mergeCell ref="J96:M96"/>
+    <mergeCell ref="N95:Q95"/>
+    <mergeCell ref="N96:Q96"/>
+    <mergeCell ref="B93:H93"/>
+    <mergeCell ref="B94:H94"/>
+    <mergeCell ref="J93:M93"/>
+    <mergeCell ref="J94:M94"/>
+    <mergeCell ref="N93:Q93"/>
+    <mergeCell ref="N94:Q94"/>
+    <mergeCell ref="T87:U87"/>
+    <mergeCell ref="T88:U88"/>
+    <mergeCell ref="T89:U89"/>
+    <mergeCell ref="V83:X83"/>
+    <mergeCell ref="U82:Z82"/>
+    <mergeCell ref="V84:X84"/>
+    <mergeCell ref="T86:U86"/>
+    <mergeCell ref="T83:U85"/>
+    <mergeCell ref="T93:U93"/>
+    <mergeCell ref="T94:U94"/>
+    <mergeCell ref="T95:U95"/>
+    <mergeCell ref="T96:U96"/>
+    <mergeCell ref="T90:U90"/>
+    <mergeCell ref="T91:U91"/>
+    <mergeCell ref="T92:U92"/>
+    <mergeCell ref="B86:H86"/>
+    <mergeCell ref="B87:H87"/>
+    <mergeCell ref="B88:H88"/>
+    <mergeCell ref="B89:H89"/>
+    <mergeCell ref="N88:Q88"/>
+    <mergeCell ref="N89:Q89"/>
+    <mergeCell ref="J86:M86"/>
+    <mergeCell ref="J87:M87"/>
+    <mergeCell ref="R83:R85"/>
+    <mergeCell ref="S83:S85"/>
+    <mergeCell ref="N83:Q85"/>
+    <mergeCell ref="N86:Q86"/>
+    <mergeCell ref="N87:Q87"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="51" fitToHeight="0" orientation="portrait" r:id="rId1"/>
